--- a/tools/importer/reports/import-homepage.report.xlsx
+++ b/tools/importer/reports/import-homepage.report.xlsx
@@ -52,7 +52,7 @@
     <t>homepage</t>
   </si>
   <si>
-    <t>2026-04-21T13:21:15.225Z</t>
+    <t>2026-04-21T16:44:24.873Z</t>
   </si>
   <si>
     <t>WKND Adventures — Bold Stories. Real Life. Wild Places.</t>
